--- a/artfynd/A 7608-2024 artfynd.xlsx
+++ b/artfynd/A 7608-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,65 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115204295</v>
+        <v>115371377</v>
       </c>
       <c r="B2" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Södra Billinge, Dreberg, Nrk</t>
+          <t>Perstorp, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507731</v>
+        <v>507757</v>
       </c>
       <c r="R2" t="n">
-        <v>6582519</v>
+        <v>6582442</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-03-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-03-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,44 +754,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skog på blockmark</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Närmast vägen torvmark med mossa, mitt på viltstig ca 25 m in i skogen,</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anneli Sjöstrand</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anneli Sjöstrand, Camilla Berglund</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115371016</v>
+        <v>115204295</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -845,19 +802,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Perstorp (Perstorp), Nrk</t>
+          <t>Södra Billinge, Dreberg, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507703</v>
+        <v>507731</v>
       </c>
       <c r="R3" t="n">
-        <v>6582397</v>
+        <v>6582519</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -884,22 +849,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,33 +873,39 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skog på blockmark</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Närmast vägen torvmark med mossa, mitt på viltstig ca 25 m in i skogen,</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anneli Sjöstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anneli Sjöstrand, Camilla Berglund</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115370313</v>
+        <v>115371016</v>
       </c>
       <c r="B4" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -964,24 +935,19 @@
           <t>3</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Perstorp (Perstorp), Nrk</t>
+          <t>Perstorp, Perstorp, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507816</v>
+        <v>507703</v>
       </c>
       <c r="R4" t="n">
-        <v>6582469</v>
+        <v>6582397</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1010,7 +976,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1020,7 +986,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,15 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115371171</v>
+        <v>115371044</v>
       </c>
       <c r="B5" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1043,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1090,19 +1051,29 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Perstorp (Perstorp), Nrk</t>
+          <t>Perstorp, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507728</v>
+        <v>507757</v>
       </c>
       <c r="R5" t="n">
-        <v>6582463</v>
+        <v>6582442</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1129,19 +1100,14 @@
           <t>2024-03-24</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-03-24</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:47</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>10-15 plantor i mossan</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,31 +1118,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115371655</v>
+        <v>115371171</v>
       </c>
       <c r="B6" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,14 +1179,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Perstorp (Perstorp), Nrk</t>
+          <t>Perstorp, Perstorp, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507720</v>
+        <v>507728</v>
       </c>
       <c r="R6" t="n">
-        <v>6582356</v>
+        <v>6582463</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1252,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1262,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1289,15 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115373508</v>
+        <v>115371655</v>
       </c>
       <c r="B7" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,24 +1293,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Perstorp, Nrk</t>
+          <t>Perstorp, Perstorp, Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507757</v>
+        <v>507720</v>
       </c>
       <c r="R7" t="n">
-        <v>6582442</v>
+        <v>6582356</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1376,9 +1332,19 @@
           <t>2024-03-24</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-03-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1393,117 +1359,15 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>115371377</v>
-      </c>
-      <c r="B8" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Perstorp, Nrk</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>507757</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6582442</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Närke</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Kil</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2024-03-24</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2024-03-24</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Mattias Drejby</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Mattias Drejby</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7608-2024 artfynd.xlsx
+++ b/artfynd/A 7608-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115371377</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115204295</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115371016</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115371044</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,6 +1277,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115371171</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1368,8 +1398,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115371655</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>